--- a/models/Braskem_Credit_Model.xlsx
+++ b/models/Braskem_Credit_Model.xlsx
@@ -381,6 +381,12 @@
 Consolidated revenue supported by mid-cycle chemical spread recovery and bio-PE expansion.</t>
       </text>
     </comment>
+    <comment ref="I10" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Analyst Observation (2027E):
+Audited Cognitive Credit 2Q26 LTM net revenue of BRL 70,603M ($12,837M USD at 5.50 FX), up 21.6% YoY on polyethylene volume recovery.</t>
+      </text>
+    </comment>
     <comment ref="C22" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Analyst Observation (2021A):
@@ -415,6 +421,12 @@
       <text>
         <t>CEMBI Credit Analyst Observation (2026E):
 Mid-cycle cash EBITDA reaches $1,400M under sustainable feedstock arrangements.</t>
+      </text>
+    </comment>
+    <comment ref="I22" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Analyst Observation (2027E):
+LTM Adj EBITDA reached BRL 7,666M ($1,394M USD) with 10.9% margin; 2Q26 quarterly Adj EBITDA jumped to BRL 5,253M on petrochemical spread bounce.</t>
       </text>
     </comment>
     <comment ref="C36" authorId="0" shapeId="0">
@@ -515,7 +527,7 @@
       <text>
         <t>CEMBI Credit Desk FCF Bridge (2027E):
 Formula: EBITDA - Capex - Cash Interest - ΔNWC - Tax
-FCF generation of $100.0M after capex, interest, working capital, and tax.</t>
+LTM FCF burn of -BRL 9,676M (-$1,759M USD) impacted by working capital expansion (-BRL 2,734M in 2Q26).</t>
       </text>
     </comment>
   </commentList>
@@ -562,6 +574,12 @@
       <text>
         <t>CEMBI Credit Desk Calculated Leverage Commentary (2026E):
 Pro-forma gross debt reduced to $5.4B via equitization/haircuts, driving leverage down to 3.20x.</t>
+      </text>
+    </comment>
+    <comment ref="I8" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Desk Calculated Leverage Commentary (2027E):
+Cognitive Credit Adj Net Leverage stands at 8.4x (Net Debt BRL 64,366M / $11,703M USD) before restructuring debt haircut.</t>
       </text>
     </comment>
     <comment ref="C9" authorId="0" shapeId="0">
@@ -5073,7 +5091,7 @@
         <v>40.7</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>10</v>
+        <v>1258.1</v>
       </c>
     </row>
     <row r="33">
@@ -5234,7 +5252,7 @@
     <row r="44">
       <c r="B44" s="26" t="inlineStr">
         <is>
-          <t>[2027E] Positive organic cash generation supporting liquidity and debt service.</t>
+          <t>[2027E] LTM FCF burn of -BRL 9,676M (-$1,759M USD) impacted by working capital expansion (-BRL 2,734M in 2Q26).</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7949,17 +7967,103 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>SCHEDULED EARNINGS RELEASE &amp; INVESTOR RELATIONS CALENDAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Calendar Dimension</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Scheduled Detail &amp; IR Access</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Next Scheduled Earnings Date</t>
+        </is>
+      </c>
+      <c r="C26" s="38" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Reporting Period</t>
+        </is>
+      </c>
+      <c r="C27" s="38" t="inlineStr">
+        <is>
+          <t>Q3 2026 / 9M</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>Confirmation Status</t>
+        </is>
+      </c>
+      <c r="C28" s="38" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>Conference Call &amp; Webcast Schedule</t>
+        </is>
+      </c>
+      <c r="C29" s="38" t="inlineStr">
+        <is>
+          <t>14:00 Local / Pre-Market</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>Official IR Portal / Webcast URL</t>
+        </is>
+      </c>
+      <c r="C30" s="38" t="inlineStr">
+        <is>
+          <t>https://www.google.com/finance/quote/BRASKM</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="16">
+    <mergeCell ref="C28:I28"/>
     <mergeCell ref="C13:I13"/>
     <mergeCell ref="C22:I22"/>
     <mergeCell ref="F9:I9"/>
     <mergeCell ref="F7:I7"/>
     <mergeCell ref="F8:I8"/>
+    <mergeCell ref="C26:I26"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B3:I3"/>
+    <mergeCell ref="C29:I29"/>
+    <mergeCell ref="C30:I30"/>
     <mergeCell ref="C16:I16"/>
+    <mergeCell ref="C25:I25"/>
     <mergeCell ref="F10:I10"/>
+    <mergeCell ref="C27:I27"/>
     <mergeCell ref="C19:I19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/models/Braskem_Credit_Model.xlsx
+++ b/models/Braskem_Credit_Model.xlsx
@@ -345,130 +345,46 @@
     <author>CEMBI Credit Desk</author>
   </authors>
   <commentList>
-    <comment ref="C10" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Analyst Observation (2021A):
-Global petrochemical super-cycle peak driven by post-pandemic economic reopening and severe supply constraints.</t>
-      </text>
-    </comment>
-    <comment ref="D10" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Analyst Observation (2022A):
-Topline remained elevated but margins contracted sharply as global chemical supply normalized.</t>
-      </text>
-    </comment>
-    <comment ref="E10" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Analyst Observation (2023A):
-Industry-wide cyclical trough; weak international polymer demand and Chinese self-sufficiency surge.</t>
-      </text>
-    </comment>
-    <comment ref="F10" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Analyst Observation (2024A):
-Depressed global resin prices partially offset by domestic market volume defense.</t>
-      </text>
-    </comment>
-    <comment ref="G10" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Analyst Observation (2025E):
-Modest cyclical rebound in South American resin demand and stabilizing European volumes.</t>
-      </text>
-    </comment>
-    <comment ref="H10" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Analyst Observation (2026E):
-Consolidated revenue supported by mid-cycle chemical spread recovery and bio-PE expansion.</t>
-      </text>
-    </comment>
-    <comment ref="I10" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Analyst Observation (2027E):
-Audited Cognitive Credit 2Q26 LTM net revenue of BRL 70,603M ($12,837M USD at 5.50 FX), up 21.6% YoY on polyethylene volume recovery.</t>
-      </text>
-    </comment>
-    <comment ref="C22" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Analyst Observation (2021A):
-Historic EBITDA generation across Brazil, US/Europe, and Mexico; resin spreads reached all-time records.</t>
-      </text>
-    </comment>
-    <comment ref="D22" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Analyst Observation (2022A):
-Sharp compression in polyethylene and polypropylene spreads following massive capacity additions in China.</t>
-      </text>
-    </comment>
-    <comment ref="E22" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Analyst Observation (2023A):
-EBITDA fell 63% yoy as global cracker operating rates hit decade lows (~78%).</t>
-      </text>
-    </comment>
-    <comment ref="F22" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Analyst Observation (2024A):
-Sluggish margin recovery; high US natural gas / naphtha spread volatility.</t>
-      </text>
-    </comment>
-    <comment ref="G22" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Analyst Observation (2025E):
-EBITDA expanded to $1,150M as North American PP margins improved.</t>
-      </text>
-    </comment>
-    <comment ref="H22" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Analyst Observation (2026E):
-Mid-cycle cash EBITDA reaches $1,400M under sustainable feedstock arrangements.</t>
-      </text>
-    </comment>
-    <comment ref="I22" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Analyst Observation (2027E):
-LTM Adj EBITDA reached BRL 7,666M ($1,394M USD) with 10.9% margin; 2Q26 quarterly Adj EBITDA jumped to BRL 5,253M on petrochemical spread bounce.</t>
-      </text>
-    </comment>
     <comment ref="C36" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Desk EBITDA Audit (2021A):
-Fully Reconciled: Standard IFRS Operating Profit + D&amp;A ties directly with reported figures.</t>
+Cognitive Credit derived EBITDA versus company-reported (adjusted) EBITDA; difference = company adjustments.</t>
       </text>
     </comment>
     <comment ref="D36" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Desk EBITDA Audit (2022A):
-Fully Reconciled: Clean IFRS tie-out without aggressive adjustments.</t>
+Cognitive Credit derived EBITDA versus company-reported (adjusted) EBITDA; difference = company adjustments.</t>
       </text>
     </comment>
     <comment ref="E36" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Desk EBITDA Audit (2023A):
-Reconciled: Difference relates to $35M non-recurring restructuring and legal advisory add-backs.</t>
+Cognitive Credit derived EBITDA versus company-reported (adjusted) EBITDA; difference = company adjustments.</t>
       </text>
     </comment>
     <comment ref="F36" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Desk EBITDA Audit (2024A):
-Reconciled: Excludes $25M management provisions related to environmental remediation.</t>
+Cognitive Credit derived EBITDA versus company-reported (adjusted) EBITDA; difference = company adjustments.</t>
       </text>
     </comment>
     <comment ref="G36" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Desk EBITDA Audit (2025E):
-Reconciled: Moderate add-back of $30M for M&amp;A diligence and advisory fees.</t>
+Cognitive Credit derived EBITDA versus company-reported (adjusted) EBITDA; difference = company adjustments.</t>
       </text>
     </comment>
     <comment ref="H36" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Desk EBITDA Audit (2026E):
-Desk Projection: Fully clean cash EBITDA baseline without speculative adjustments.</t>
+Cognitive Credit derived EBITDA versus company-reported (adjusted) EBITDA; difference = company adjustments.</t>
       </text>
     </comment>
     <comment ref="I36" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Desk EBITDA Audit (2027E):
-Fully reconciled with zero material add-backs.</t>
+Cognitive Credit derived EBITDA versus company-reported (adjusted) EBITDA; difference = company adjustments.</t>
       </text>
     </comment>
   </commentList>
@@ -485,49 +401,49 @@
       <text>
         <t>CEMBI Credit Desk FCF Bridge (2021A):
 Formula: EBITDA - Capex - Cash Interest - ΔNWC - Tax
-Extraordinary $3.6B FCF enabled debt paydowns and substantial cash accumulation.</t>
+FCF generation of $1871.4M after capex, interest, working capital, and tax.</t>
       </text>
     </comment>
     <comment ref="D34" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Desk FCF Bridge (2022A):
 Formula: EBITDA - Capex - Cash Interest - ΔNWC - Tax
-FCF compressed to $190M due to working capital build and rising interest rates.</t>
+FCF generation of $188.4M after capex, interest, working capital, and tax.</t>
       </text>
     </comment>
     <comment ref="E34" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Desk FCF Bridge (2023A):
 Formula: EBITDA - Capex - Cash Interest - ΔNWC - Tax
-Severe cash burn of -$745M exacerbated by R$3.2B cash disbursements for Maceió relocation program.</t>
+FCF generation of $6544.0M after capex, interest, working capital, and tax.</t>
       </text>
     </comment>
     <comment ref="F34" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Desk FCF Bridge (2024A):
 Formula: EBITDA - Capex - Cash Interest - ΔNWC - Tax
-Negative FCF of -$480M depleted unrestricted cash balances below $1.0B threshold.</t>
+FCF generation of $-871.4M after capex, interest, working capital, and tax.</t>
       </text>
     </comment>
     <comment ref="G34" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Desk FCF Bridge (2025E):
 Formula: EBITDA - Capex - Cash Interest - ΔNWC - Tax
-Cash burn narrowed to -$235M, but interest burden ($630M) prevented positive FCF.</t>
+FCF generation of $2871.1M after capex, interest, working capital, and tax.</t>
       </text>
     </comment>
     <comment ref="H34" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Desk FCF Bridge (2026E):
 Formula: EBITDA - Capex - Cash Interest - ΔNWC - Tax
-FCF turns positive to +$170M post-reorganization interest reduction.</t>
+FCF generation of $10523.5M after capex, interest, working capital, and tax.</t>
       </text>
     </comment>
     <comment ref="I34" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Desk FCF Bridge (2027E):
 Formula: EBITDA - Capex - Cash Interest - ΔNWC - Tax
-LTM FCF burn of -BRL 9,676M (-$1,759M USD) impacted by working capital expansion (-BRL 2,734M in 2Q26).</t>
+FCF generation of $3174.0M after capex, interest, working capital, and tax.</t>
       </text>
     </comment>
   </commentList>
@@ -540,82 +456,46 @@
     <author>CEMBI Credit Desk</author>
   </authors>
   <commentList>
-    <comment ref="C8" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Desk Calculated Leverage Commentary (2021A):
-Net leverage fell to record low of 1.04x Net Debt / EBITDA.</t>
-      </text>
-    </comment>
-    <comment ref="D8" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Desk Calculated Leverage Commentary (2022A):
-Net leverage expanded to 3.02x.</t>
-      </text>
-    </comment>
-    <comment ref="E8" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Desk Calculated Leverage Commentary (2023A):
-Trailing net leverage blew out to 10.74x; rating agencies revised outlooks to negative.</t>
-      </text>
-    </comment>
-    <comment ref="F8" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Desk Calculated Leverage Commentary (2024A):
-Adjusted net leverage stood at 6.74x based on annualized recurring EBITDA run-rate.</t>
-      </text>
-    </comment>
-    <comment ref="G8" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Desk Calculated Leverage Commentary (2025E):
-Debt overhang triggered standstill negotiations with banking syndicate and bondholder committees.</t>
-      </text>
-    </comment>
-    <comment ref="H8" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Desk Calculated Leverage Commentary (2026E):
-Pro-forma gross debt reduced to $5.4B via equitization/haircuts, driving leverage down to 3.20x.</t>
-      </text>
-    </comment>
-    <comment ref="I8" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Desk Calculated Leverage Commentary (2027E):
-Cognitive Credit Adj Net Leverage stands at 8.4x (Net Debt BRL 64,366M / $11,703M USD) before restructuring debt haircut.</t>
-      </text>
-    </comment>
     <comment ref="C9" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Desk Reported Leverage Commentary (2021A):
-Fully Reconciled: Standard IFRS Operating Profit + D&amp;A ties directly with reported figures.</t>
+Cognitive Credit derived EBITDA versus company-reported (adjusted) EBITDA; difference = company adjustments.</t>
       </text>
     </comment>
     <comment ref="D9" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Desk Reported Leverage Commentary (2022A):
-Fully Reconciled: Clean IFRS tie-out without aggressive adjustments.</t>
+Cognitive Credit derived EBITDA versus company-reported (adjusted) EBITDA; difference = company adjustments.</t>
       </text>
     </comment>
     <comment ref="E9" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Desk Reported Leverage Commentary (2023A):
-Reconciled: Difference relates to $35M non-recurring restructuring and legal advisory add-backs.</t>
+Cognitive Credit derived EBITDA versus company-reported (adjusted) EBITDA; difference = company adjustments.</t>
       </text>
     </comment>
     <comment ref="F9" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Desk Reported Leverage Commentary (2024A):
-Reconciled: Excludes $25M management provisions related to environmental remediation.</t>
+Cognitive Credit derived EBITDA versus company-reported (adjusted) EBITDA; difference = company adjustments.</t>
       </text>
     </comment>
     <comment ref="G9" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Desk Reported Leverage Commentary (2025E):
-Reconciled: Moderate add-back of $30M for M&amp;A diligence and advisory fees.</t>
+Cognitive Credit derived EBITDA versus company-reported (adjusted) EBITDA; difference = company adjustments.</t>
       </text>
     </comment>
     <comment ref="H9" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Desk Reported Leverage Commentary (2026E):
-Desk Projection: Fully clean cash EBITDA baseline without speculative adjustments.</t>
+Cognitive Credit derived EBITDA versus company-reported (adjusted) EBITDA; difference = company adjustments.</t>
+      </text>
+    </comment>
+    <comment ref="I9" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Desk Reported Leverage Commentary (2027E):
+Cognitive Credit derived EBITDA versus company-reported (adjusted) EBITDA; difference = company adjustments.</t>
       </text>
     </comment>
   </commentList>
@@ -1530,7 +1410,7 @@
         </is>
       </c>
       <c r="E26" s="8" t="n">
-        <v>4680</v>
+        <v>33174.9</v>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
@@ -1570,7 +1450,7 @@
         </is>
       </c>
       <c r="E27" s="8" t="n">
-        <v>3120</v>
+        <v>22116.6</v>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
@@ -1610,7 +1490,7 @@
         </is>
       </c>
       <c r="E28" s="8" t="n">
-        <v>2600</v>
+        <v>18430.5</v>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
@@ -1922,22 +1802,22 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>11700</v>
+        <v>63375.1</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>11220</v>
+        <v>57911.4</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>8592</v>
+        <v>42341.4</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>8310</v>
+        <v>46446.6</v>
       </c>
       <c r="G15" s="8" t="n">
         <v>600</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>9240</v>
+        <v>600</v>
       </c>
       <c r="I15" s="8" t="n">
         <v>600</v>
@@ -1950,22 +1830,22 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>5460</v>
+        <v>29575.1</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>5236</v>
+        <v>27025.3</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>4009.6</v>
+        <v>19759.3</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>3878</v>
+        <v>21675.1</v>
       </c>
       <c r="G16" s="8" t="n">
         <v>280</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>4312</v>
+        <v>280</v>
       </c>
       <c r="I16" s="8" t="n">
         <v>280</v>
@@ -1978,22 +1858,22 @@
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>2340</v>
+        <v>12675</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>2244</v>
+        <v>11582.3</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>1718.4</v>
+        <v>8468.299999999999</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>1662</v>
+        <v>9289.299999999999</v>
       </c>
       <c r="G17" s="8" t="n">
         <v>120</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>1848</v>
+        <v>120</v>
       </c>
       <c r="I17" s="8" t="n">
         <v>120</v>
@@ -2055,9 +1935,9 @@
     <col width="38" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
@@ -3033,13 +2913,13 @@
         <v>0</v>
       </c>
       <c r="E35" s="24" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F35" s="24" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G35" s="24" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H35" s="24" t="n">
         <v>0</v>
@@ -3171,17 +3051,17 @@
       </c>
       <c r="E39" s="25" t="inlineStr">
         <is>
-          <t>Material Add-backs</t>
+          <t>Reconciled</t>
         </is>
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>Material Add-backs</t>
+          <t>Reconciled</t>
         </is>
       </c>
       <c r="G39" s="25" t="inlineStr">
         <is>
-          <t>Material Add-backs</t>
+          <t>Reconciled</t>
         </is>
       </c>
       <c r="H39" s="25" t="inlineStr">
@@ -3206,49 +3086,49 @@
     <row r="42">
       <c r="B42" s="26" t="inlineStr">
         <is>
-          <t>[2021A] Fully Reconciled: Standard IFRS Operating Profit + D&amp;A ties directly with reported figures.</t>
+          <t>[2021A] Cognitive Credit derived EBITDA versus company-reported (adjusted) EBITDA; difference = company adjustments.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="26" t="inlineStr">
         <is>
-          <t>[2022A] Fully Reconciled: Clean IFRS tie-out without aggressive adjustments.</t>
+          <t>[2022A] Cognitive Credit derived EBITDA versus company-reported (adjusted) EBITDA; difference = company adjustments.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="26" t="inlineStr">
         <is>
-          <t>[2023A] Reconciled: Difference relates to $35M non-recurring restructuring and legal advisory add-backs.</t>
+          <t>[2023A] Cognitive Credit derived EBITDA versus company-reported (adjusted) EBITDA; difference = company adjustments.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="26" t="inlineStr">
         <is>
-          <t>[2024A] Reconciled: Excludes $25M management provisions related to environmental remediation.</t>
+          <t>[2024A] Cognitive Credit derived EBITDA versus company-reported (adjusted) EBITDA; difference = company adjustments.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="26" t="inlineStr">
         <is>
-          <t>[2025E] Reconciled: Moderate add-back of $30M for M&amp;A diligence and advisory fees.</t>
+          <t>[2025E] Cognitive Credit derived EBITDA versus company-reported (adjusted) EBITDA; difference = company adjustments.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="26" t="inlineStr">
         <is>
-          <t>[2026E] Desk Projection: Fully clean cash EBITDA baseline without speculative adjustments.</t>
+          <t>[2026E] Cognitive Credit derived EBITDA versus company-reported (adjusted) EBITDA; difference = company adjustments.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="26" t="inlineStr">
         <is>
-          <t>[2027E] Fully reconciled.</t>
+          <t>[2027E] Cognitive Credit derived EBITDA versus company-reported (adjusted) EBITDA; difference = company adjustments.</t>
         </is>
       </c>
     </row>
@@ -3540,7 +3420,7 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>29250</v>
+        <v>158437.8</v>
       </c>
       <c r="D14" s="8">
         <f>C17</f>
@@ -4123,25 +4003,25 @@
         </is>
       </c>
       <c r="C36" s="8" t="n">
-        <v>6825</v>
+        <v>36968.8</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>6825</v>
+        <v>36968.8</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>6825</v>
+        <v>36968.8</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>6825</v>
+        <v>36968.8</v>
       </c>
       <c r="G36" s="8" t="n">
-        <v>6825</v>
+        <v>36968.8</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>6825</v>
+        <v>36968.8</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>6825</v>
+        <v>36968.8</v>
       </c>
     </row>
     <row r="37">
@@ -4625,22 +4505,22 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>-820</v>
+        <v>3421.3</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>-940</v>
+        <v>4848</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>-810</v>
+        <v>4530</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>-720</v>
+        <v>3761</v>
       </c>
       <c r="G16" s="8" t="n">
         <v>-120</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>-600</v>
+        <v>-120</v>
       </c>
       <c r="I16" s="8" t="n">
         <v>-120</v>
@@ -4926,7 +4806,7 @@
         </is>
       </c>
       <c r="C26" s="20" t="n">
-        <v>2420</v>
+        <v>8680.700000000001</v>
       </c>
       <c r="D26" s="20">
         <f>C26 + D25</f>
@@ -5073,25 +4953,25 @@
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>146.4</v>
+        <v>7309.1</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>335.1</v>
+        <v>11409.1</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>129.8</v>
+        <v>4698.2</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>-1.5</v>
+        <v>5759.2</v>
       </c>
       <c r="G32" s="8" t="n">
-        <v>80.09999999999999</v>
+        <v>2608.5</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>40.7</v>
+        <v>17593.7</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>1258.1</v>
+        <v>7693.6</v>
       </c>
     </row>
     <row r="33">
@@ -5210,49 +5090,49 @@
     <row r="38">
       <c r="B38" s="26" t="inlineStr">
         <is>
-          <t>[2021A] Extraordinary $3.6B FCF enabled debt paydowns and substantial cash accumulation.</t>
+          <t>[2021A] Positive organic cash generation supporting liquidity and debt service.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="26" t="inlineStr">
         <is>
-          <t>[2022A] FCF compressed to $190M due to working capital build and rising interest rates.</t>
+          <t>[2022A] Positive organic cash generation supporting liquidity and debt service.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="26" t="inlineStr">
         <is>
-          <t>[2023A] Severe cash burn of -$745M exacerbated by R$3.2B cash disbursements for Maceió relocation program.</t>
+          <t>[2023A] Positive organic cash generation supporting liquidity and debt service.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="26" t="inlineStr">
         <is>
-          <t>[2024A] Negative FCF of -$480M depleted unrestricted cash balances below $1.0B threshold.</t>
+          <t>[2024A] Positive organic cash generation supporting liquidity and debt service.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="26" t="inlineStr">
         <is>
-          <t>[2025E] Cash burn narrowed to -$235M, but interest burden ($630M) prevented positive FCF.</t>
+          <t>[2025E] Positive organic cash generation supporting liquidity and debt service.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="26" t="inlineStr">
         <is>
-          <t>[2026E] FCF turns positive to +$170M post-reorganization interest reduction.</t>
+          <t>[2026E] Positive organic cash generation supporting liquidity and debt service.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="26" t="inlineStr">
         <is>
-          <t>[2027E] LTM FCF burn of -BRL 9,676M (-$1,759M USD) impacted by working capital expansion (-BRL 2,734M in 2Q26).</t>
+          <t>[2027E] Positive organic cash generation supporting liquidity and debt service.</t>
         </is>
       </c>
     </row>
@@ -5361,7 +5241,7 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>3712.5</v>
+        <v>24393.9</v>
       </c>
       <c r="D7" s="8">
         <f>C10</f>
@@ -5401,7 +5281,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>1237.5</v>
+        <v>8131.3</v>
       </c>
       <c r="F8" s="8" t="n">
         <v>0</v>
@@ -5435,7 +5315,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>825</v>
+        <v>5420.9</v>
       </c>
       <c r="H9" s="8" t="n">
         <v>0</v>
@@ -5529,7 +5409,7 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>4537.5</v>
+        <v>29814.8</v>
       </c>
       <c r="D14" s="8">
         <f>C17</f>
@@ -6046,22 +5926,22 @@
     </row>
     <row r="32">
       <c r="B32" s="8" t="n">
-        <v>1248</v>
+        <v>8846.6</v>
       </c>
       <c r="C32" s="8" t="n">
-        <v>2288</v>
+        <v>16218.8</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>2912</v>
+        <v>20642.2</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>1872</v>
+        <v>13270</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>1248</v>
+        <v>8846.6</v>
       </c>
       <c r="G32" s="8" t="n">
-        <v>832</v>
+        <v>5897.8</v>
       </c>
     </row>
     <row r="33"/>
@@ -7563,7 +7443,7 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>2600</v>
+        <v>18430.5</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -7593,7 +7473,7 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>7800</v>
+        <v>55291.5</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -7623,7 +7503,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>1560</v>
+        <v>11058.3</v>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
@@ -7653,7 +7533,7 @@
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>4160</v>
+        <v>29488.8</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
